--- a/ConfigExporter/xlsx/replay_config.xlsx
+++ b/ConfigExporter/xlsx/replay_config.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.875" customWidth="1" min="1" max="1"/>
@@ -1619,6 +1619,406 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aiPcTier1MaxVisits9</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>400</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PC 9 路 AI 推荐第一档快速访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>aiPcTier1MaxVisits13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>300</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PC 13 路 AI 推荐第一档快速访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>aiPcTier1MaxVisits19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>160</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PC 19 路 AI 推荐第一档快速访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>aiPcTier2MaxVisits9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PC 9 路 AI 推荐第二档 ownership 访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>aiPcTier2MaxVisits13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>900</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PC 13 路 AI 推荐第二档 ownership 访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aiPcTier2MaxVisits19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>500</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PC 19 路 AI 推荐第二档 ownership 访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aiPcTier3MaxVisits9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PC 9 路 AI 推荐第三档最终访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aiPcTier3MaxVisits13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PC 13 路 AI 推荐第三档最终访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>aiPcTier3MaxVisits19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PC 19 路 AI 推荐第三档最终访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aiPcWideRootNoise</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ai_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PC AI 推荐请求 wideRootNoise</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>chartPcLowMaxVisits9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>120</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PC 9 路复盘曲线低精度访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>chartPcLowMaxVisits13</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>96</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PC 13 路复盘曲线低精度访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>chartPcLowMaxVisits19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>72</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PC 19 路复盘曲线低精度访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>chartPcHighMaxVisits9</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>600</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PC 9 路复盘曲线高精度访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>chartPcHighMaxVisits13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>480</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PC 13 路复盘曲线高精度访问次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>chartPcHighMaxVisits19</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>chart_analysis_pc</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>320</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PC 19 路复盘曲线高精度访问次数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
